--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:28</t>
+    <t xml:space="preserve">2026-09-12 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:45</t>
+    <t xml:space="preserve">2026-09-24 00:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:22</t>
+    <t xml:space="preserve">2026-09-27 22:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:11</t>
+    <t xml:space="preserve">2026-10-01 20:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:52</t>
+    <t xml:space="preserve">2026-10-02 13:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">San Pedro de la Paz</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Cabrero</t>
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Tucapel</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:18</t>
+    <t xml:space="preserve">2026-10-04 08:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2021_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:05</t>
+    <t xml:space="preserve">2026-10-05 07:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
